--- a/GuardianShield_Transaction_Ledger.xlsx
+++ b/GuardianShield_Transaction_Ledger.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger Audit Track" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ledger Audit Track" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,15 +488,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -727,6 +727,174 @@
         <v>55</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>U101</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15:18:14</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>U103</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>U104</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15:25:54</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>U104</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>U103</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15:28:54</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>U103</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>U104</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15:29:51</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>U109</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>U110</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15:31:27</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>U110</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>U109</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15:32:53</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GuardianShield_Transaction_Ledger.xlsx
+++ b/GuardianShield_Transaction_Ledger.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -895,6 +895,118 @@
         <v>60</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>U101</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16:04:57</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>U101</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16:05:12</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>U101</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16:15:17</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>U105</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16:16:17</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
